--- a/artfynd/A 17445-2026 artfynd.xlsx
+++ b/artfynd/A 17445-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128980889</v>
+        <v>128980933</v>
       </c>
       <c r="B2" t="n">
-        <v>92003</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582155</v>
+        <v>582171</v>
       </c>
       <c r="R2" t="n">
-        <v>7051036</v>
+        <v>7051059</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128981181</v>
+        <v>128980894</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,43 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kullaberget, Kullaberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582173</v>
+        <v>582160</v>
       </c>
       <c r="R3" t="n">
-        <v>7050946</v>
+        <v>7051050</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128981008</v>
+        <v>128980889</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kullaberget, Kullaberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582124</v>
+        <v>582155</v>
       </c>
       <c r="R4" t="n">
-        <v>7051046</v>
+        <v>7051036</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128980894</v>
+        <v>128980849</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582160</v>
+        <v>582143</v>
       </c>
       <c r="R5" t="n">
-        <v>7051050</v>
+        <v>7050994</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128980849</v>
+        <v>128981233</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1152,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582143</v>
+        <v>582144</v>
       </c>
       <c r="R6" t="n">
-        <v>7050994</v>
+        <v>7050925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,48 +1210,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128980933</v>
+        <v>128981008</v>
       </c>
       <c r="B7" t="n">
-        <v>91848</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kullaberget, Kullaberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582171</v>
+        <v>582124</v>
       </c>
       <c r="R7" t="n">
-        <v>7051059</v>
+        <v>7051046</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,6 +1319,122 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128981181</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kullaberget, Kullaberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>582173</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7050946</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17445-2026 artfynd.xlsx
+++ b/artfynd/A 17445-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980933</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980894</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980849</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128981233</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128981008</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,8 +1470,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128981181</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>